--- a/web/templates/Project5/David_version/05_Dataset_rawBlankmass.xlsx
+++ b/web/templates/Project5/David_version/05_Dataset_rawBlankmass.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haixi\Documents\DataHarmonizerDevelop\web\templates\Project5\David\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haixi\Documents\DataHarmonizerDevelop\web\templates\Project5\David_version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404DAD08-75E4-4B0F-B1A0-E9EFC3630741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D48A976-B6C1-4C2A-88D6-5CE683904EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="05_Dataset_rawBlankmass" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/web/templates/Project5/David_version/05_Dataset_rawBlankmass.xlsx
+++ b/web/templates/Project5/David_version/05_Dataset_rawBlankmass.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haixi\Documents\DataHarmonizerDevelop\web\templates\Project5\David_version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D48A976-B6C1-4C2A-88D6-5CE683904EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F983F68-95D6-4192-8E2A-795CA2F07E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,9 +39,6 @@
     <t>tPCB</t>
   </si>
   <si>
-    <t>PCB_141</t>
-  </si>
-  <si>
     <t>B1</t>
   </si>
   <si>
@@ -601,6 +598,9 @@
   </si>
   <si>
     <t>PCB209</t>
+  </si>
+  <si>
+    <t>PCB141</t>
   </si>
 </sst>
 </file>
@@ -940,534 +940,534 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>25</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>26</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>27</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>28</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>29</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>30</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>32</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>33</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>34</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>35</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>36</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>37</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>38</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>39</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>40</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>42</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>43</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>44</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>45</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>46</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>47</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>48</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>49</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>50</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>51</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>52</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>53</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>54</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>55</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>56</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>57</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>58</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>59</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>60</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>61</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>62</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>63</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>64</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>65</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>66</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>67</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>68</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>69</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>70</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>71</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>72</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>73</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>74</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>75</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>76</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>77</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>78</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>79</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>80</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>81</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>82</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>83</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>84</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>85</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>86</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>87</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>88</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>89</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>90</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>91</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BZ1" t="s">
         <v>92</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" t="s">
         <v>93</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CB1" t="s">
         <v>94</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>95</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>96</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>97</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>98</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>99</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>100</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>101</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CJ1" t="s">
         <v>102</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CK1" t="s">
         <v>103</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CL1" t="s">
         <v>104</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CM1" t="s">
         <v>105</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CN1" t="s">
         <v>106</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CO1" t="s">
         <v>107</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CP1" t="s">
         <v>108</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CQ1" t="s">
         <v>109</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CR1" t="s">
         <v>110</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CS1" t="s">
         <v>111</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CT1" t="s">
         <v>112</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>113</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>114</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>115</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
         <v>116</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CY1" t="s">
         <v>117</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CZ1" t="s">
         <v>118</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DA1" t="s">
         <v>119</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DB1" t="s">
         <v>120</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DC1" t="s">
         <v>121</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DD1" t="s">
         <v>122</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DE1" t="s">
         <v>123</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DF1" t="s">
         <v>124</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DG1" t="s">
         <v>125</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DH1" t="s">
         <v>126</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="DI1" t="s">
         <v>127</v>
       </c>
-      <c r="DI1" t="s">
+      <c r="DJ1" t="s">
         <v>128</v>
       </c>
-      <c r="DJ1" t="s">
+      <c r="DK1" t="s">
         <v>129</v>
       </c>
-      <c r="DK1" t="s">
+      <c r="DL1" t="s">
         <v>130</v>
       </c>
-      <c r="DL1" t="s">
+      <c r="DM1" t="s">
         <v>131</v>
       </c>
-      <c r="DM1" t="s">
+      <c r="DN1" t="s">
         <v>132</v>
       </c>
-      <c r="DN1" t="s">
+      <c r="DO1" t="s">
+        <v>191</v>
+      </c>
+      <c r="DP1" t="s">
         <v>133</v>
       </c>
-      <c r="DO1" t="s">
-        <v>4</v>
-      </c>
-      <c r="DP1" t="s">
+      <c r="DQ1" t="s">
         <v>134</v>
       </c>
-      <c r="DQ1" t="s">
+      <c r="DR1" t="s">
         <v>135</v>
       </c>
-      <c r="DR1" t="s">
+      <c r="DS1" t="s">
         <v>136</v>
       </c>
-      <c r="DS1" t="s">
+      <c r="DT1" t="s">
         <v>137</v>
       </c>
-      <c r="DT1" t="s">
+      <c r="DU1" t="s">
         <v>138</v>
       </c>
-      <c r="DU1" t="s">
+      <c r="DV1" t="s">
         <v>139</v>
       </c>
-      <c r="DV1" t="s">
+      <c r="DW1" t="s">
         <v>140</v>
       </c>
-      <c r="DW1" t="s">
+      <c r="DX1" t="s">
         <v>141</v>
       </c>
-      <c r="DX1" t="s">
+      <c r="DY1" t="s">
         <v>142</v>
       </c>
-      <c r="DY1" t="s">
+      <c r="DZ1" t="s">
         <v>143</v>
       </c>
-      <c r="DZ1" t="s">
+      <c r="EA1" t="s">
         <v>144</v>
       </c>
-      <c r="EA1" t="s">
+      <c r="EB1" t="s">
         <v>145</v>
       </c>
-      <c r="EB1" t="s">
+      <c r="EC1" t="s">
         <v>146</v>
       </c>
-      <c r="EC1" t="s">
+      <c r="ED1" t="s">
         <v>147</v>
       </c>
-      <c r="ED1" t="s">
+      <c r="EE1" t="s">
         <v>148</v>
       </c>
-      <c r="EE1" t="s">
+      <c r="EF1" t="s">
         <v>149</v>
       </c>
-      <c r="EF1" t="s">
+      <c r="EG1" t="s">
         <v>150</v>
       </c>
-      <c r="EG1" t="s">
+      <c r="EH1" t="s">
         <v>151</v>
       </c>
-      <c r="EH1" t="s">
+      <c r="EI1" t="s">
         <v>152</v>
       </c>
-      <c r="EI1" t="s">
+      <c r="EJ1" t="s">
         <v>153</v>
       </c>
-      <c r="EJ1" t="s">
+      <c r="EK1" t="s">
         <v>154</v>
       </c>
-      <c r="EK1" t="s">
+      <c r="EL1" t="s">
         <v>155</v>
       </c>
-      <c r="EL1" t="s">
+      <c r="EM1" t="s">
         <v>156</v>
       </c>
-      <c r="EM1" t="s">
+      <c r="EN1" t="s">
         <v>157</v>
       </c>
-      <c r="EN1" t="s">
+      <c r="EO1" t="s">
         <v>158</v>
       </c>
-      <c r="EO1" t="s">
+      <c r="EP1" t="s">
         <v>159</v>
       </c>
-      <c r="EP1" t="s">
+      <c r="EQ1" t="s">
         <v>160</v>
       </c>
-      <c r="EQ1" t="s">
+      <c r="ER1" t="s">
         <v>161</v>
       </c>
-      <c r="ER1" t="s">
+      <c r="ES1" t="s">
         <v>162</v>
       </c>
-      <c r="ES1" t="s">
+      <c r="ET1" t="s">
         <v>163</v>
       </c>
-      <c r="ET1" t="s">
+      <c r="EU1" t="s">
         <v>164</v>
       </c>
-      <c r="EU1" t="s">
+      <c r="EV1" t="s">
         <v>165</v>
       </c>
-      <c r="EV1" t="s">
+      <c r="EW1" t="s">
         <v>166</v>
       </c>
-      <c r="EW1" t="s">
+      <c r="EX1" t="s">
         <v>167</v>
       </c>
-      <c r="EX1" t="s">
+      <c r="EY1" t="s">
         <v>168</v>
       </c>
-      <c r="EY1" t="s">
+      <c r="EZ1" t="s">
         <v>169</v>
       </c>
-      <c r="EZ1" t="s">
+      <c r="FA1" t="s">
         <v>170</v>
       </c>
-      <c r="FA1" t="s">
+      <c r="FB1" t="s">
         <v>171</v>
       </c>
-      <c r="FB1" t="s">
+      <c r="FC1" t="s">
         <v>172</v>
       </c>
-      <c r="FC1" t="s">
+      <c r="FD1" t="s">
         <v>173</v>
       </c>
-      <c r="FD1" t="s">
+      <c r="FE1" t="s">
         <v>174</v>
       </c>
-      <c r="FE1" t="s">
+      <c r="FF1" t="s">
         <v>175</v>
       </c>
-      <c r="FF1" t="s">
+      <c r="FG1" t="s">
         <v>176</v>
       </c>
-      <c r="FG1" t="s">
+      <c r="FH1" t="s">
         <v>177</v>
       </c>
-      <c r="FH1" t="s">
+      <c r="FI1" t="s">
         <v>178</v>
       </c>
-      <c r="FI1" t="s">
+      <c r="FJ1" t="s">
         <v>179</v>
       </c>
-      <c r="FJ1" t="s">
+      <c r="FK1" t="s">
         <v>180</v>
       </c>
-      <c r="FK1" t="s">
+      <c r="FL1" t="s">
         <v>181</v>
       </c>
-      <c r="FL1" t="s">
+      <c r="FM1" t="s">
         <v>182</v>
       </c>
-      <c r="FM1" t="s">
+      <c r="FN1" t="s">
         <v>183</v>
       </c>
-      <c r="FN1" t="s">
+      <c r="FO1" t="s">
         <v>184</v>
       </c>
-      <c r="FO1" t="s">
+      <c r="FP1" t="s">
         <v>185</v>
       </c>
-      <c r="FP1" t="s">
+      <c r="FQ1" t="s">
         <v>186</v>
       </c>
-      <c r="FQ1" t="s">
+      <c r="FR1" t="s">
         <v>187</v>
       </c>
-      <c r="FR1" t="s">
+      <c r="FS1" t="s">
         <v>188</v>
       </c>
-      <c r="FS1" t="s">
+      <c r="FT1" t="s">
         <v>189</v>
       </c>
-      <c r="FT1" t="s">
+      <c r="FU1" t="s">
         <v>190</v>
-      </c>
-      <c r="FU1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:177" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
       </c>
       <c r="D2">
         <v>21.839878741427722</v>
@@ -1994,13 +1994,13 @@
     </row>
     <row r="3" spans="1:177" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
       </c>
       <c r="D3">
         <v>16.861134715052394</v>
@@ -2527,13 +2527,13 @@
     </row>
     <row r="4" spans="1:177" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
       </c>
       <c r="D4">
         <v>25.452659030870016</v>
@@ -3060,13 +3060,13 @@
     </row>
     <row r="5" spans="1:177" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
         <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
       </c>
       <c r="D5">
         <v>17.896412758686445</v>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="6" spans="1:177" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
         <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
       </c>
       <c r="D6">
         <v>18.654283892060558</v>
@@ -4126,13 +4126,13 @@
     </row>
     <row r="7" spans="1:177" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
         <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
       </c>
       <c r="D7">
         <v>43.067686783838283</v>
@@ -4659,13 +4659,13 @@
     </row>
     <row r="8" spans="1:177" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
         <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
       </c>
       <c r="D8">
         <v>69.241403430114175</v>
@@ -5192,13 +5192,13 @@
     </row>
     <row r="9" spans="1:177" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
         <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
       </c>
       <c r="D9">
         <v>49.355483540166951</v>
@@ -5725,13 +5725,13 @@
     </row>
     <row r="10" spans="1:177" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
       </c>
       <c r="D10">
         <v>0.10876623938912329</v>
@@ -6258,13 +6258,13 @@
     </row>
     <row r="11" spans="1:177" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
         <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>17</v>
       </c>
       <c r="D11">
         <v>0.10210592705099059</v>
@@ -6791,13 +6791,13 @@
     </row>
     <row r="12" spans="1:177" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
         <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>17</v>
       </c>
       <c r="D12">
         <v>8.013476086751127E-2</v>
